--- a/docs/calibration/figures/jh4_shmtrace_full/tables.xlsx
+++ b/docs/calibration/figures/jh4_shmtrace_full/tables.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Run" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Samples" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Groups" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Variants" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Positional" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Spectrum" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Samples" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Groups" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variants" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Positional" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spectrum" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO7"/>
+  <dimension ref="A1:AP7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -595,19 +595,20 @@
     <col width="19" customWidth="1" min="26" max="26"/>
     <col width="28" customWidth="1" min="27" max="27"/>
     <col width="25" customWidth="1" min="28" max="28"/>
-    <col width="19" customWidth="1" min="29" max="29"/>
-    <col width="25" customWidth="1" min="30" max="30"/>
-    <col width="10" customWidth="1" min="31" max="31"/>
-    <col width="17" customWidth="1" min="32" max="32"/>
-    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="28" customWidth="1" min="29" max="29"/>
+    <col width="19" customWidth="1" min="30" max="30"/>
+    <col width="25" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
+    <col width="17" customWidth="1" min="33" max="33"/>
     <col width="11" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
-    <col width="19" customWidth="1" min="36" max="36"/>
-    <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="13" customWidth="1" min="38" max="38"/>
-    <col width="11" customWidth="1" min="39" max="39"/>
-    <col width="12" customWidth="1" min="40" max="40"/>
-    <col width="10" customWidth="1" min="41" max="41"/>
+    <col width="11" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="19" customWidth="1" min="37" max="37"/>
+    <col width="17" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
+    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="10" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -753,65 +754,70 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>mutation_frequency_observed_x1e3</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>mutated_reads_pct</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>mean_mutations_per_read</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pct_GC</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pct_transitions</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pct_CT_GA</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>s5f_index</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>s5f_p</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>pct_GC_in_WRC_GYW</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>pct_AT_in_WA_TW</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>analysed_bp</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>null_from</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>model_used</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>warnings</t>
         </is>
@@ -838,19 +844,19 @@
         <v>266</v>
       </c>
       <c r="F2" t="n">
-        <v>46.794</v>
+        <v>46.795</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1759</v>
+        <v>0.175921</v>
       </c>
       <c r="H2" t="n">
-        <v>48.033</v>
+        <v>48.173</v>
       </c>
       <c r="I2" t="n">
-        <v>46.794</v>
+        <v>46.795</v>
       </c>
       <c r="J2" t="n">
-        <v>49.938</v>
+        <v>50.296</v>
       </c>
       <c r="K2" t="n">
         <v>226</v>
@@ -859,19 +865,19 @@
         <v>18</v>
       </c>
       <c r="M2" t="n">
-        <v>12.019</v>
+        <v>11.351</v>
       </c>
       <c r="N2" t="n">
-        <v>7.04</v>
+        <v>7.83</v>
       </c>
       <c r="O2" t="n">
-        <v>1.238</v>
+        <v>1.377</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.667</v>
+        <v>-0.345</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.144</v>
+        <v>3.501</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -892,40 +898,43 @@
         <v>1.546</v>
       </c>
       <c r="AC2" t="n">
+        <v>1.5516</v>
+      </c>
+      <c r="AD2" t="n">
         <v>28.2</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>1.764</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AF2" t="n">
         <v>33.1</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AG2" t="n">
         <v>46.6</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AH2" t="n">
         <v>16.5</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AK2" t="n">
         <v>59.1</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AL2" t="n">
         <v>70.2</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AM2" t="n">
         <v>1141</v>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>KO1+KO2+KO3</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>quality_calibrated</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>one clone holds 81% of the reads with a junction; read-weighted numbers are dominated by it, so compare clone_weighted_frequency_x1e3</t>
         </is>
@@ -952,19 +961,19 @@
         <v>454</v>
       </c>
       <c r="F3" t="n">
-        <v>80.742</v>
+        <v>80.736</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1778</v>
+        <v>0.177832</v>
       </c>
       <c r="H3" t="n">
-        <v>80.742</v>
+        <v>80.736</v>
       </c>
       <c r="I3" t="n">
-        <v>80.742</v>
+        <v>80.736</v>
       </c>
       <c r="J3" t="n">
-        <v>80.742</v>
+        <v>80.736</v>
       </c>
       <c r="K3" t="n">
         <v>436</v>
@@ -973,19 +982,19 @@
         <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>11.889</v>
+        <v>8.917</v>
       </c>
       <c r="N3" t="n">
-        <v>-10.51</v>
+        <v>-7</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.869</v>
+        <v>-1.245</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.954</v>
+        <v>-2.218</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.784</v>
+        <v>-0.075</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -1006,40 +1015,43 @@
         <v>12.6363</v>
       </c>
       <c r="AC3" t="n">
+        <v>12.8199</v>
+      </c>
+      <c r="AD3" t="n">
         <v>92.2</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AE3" t="n">
         <v>14.418</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AF3" t="n">
         <v>31.3</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AG3" t="n">
         <v>47.8</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AH3" t="n">
         <v>15.2</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AK3" t="n">
         <v>50.7</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AL3" t="n">
         <v>73.09999999999999</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AM3" t="n">
         <v>1141</v>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>KO1+KO2+KO3</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>quality_calibrated</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1062,19 +1074,19 @@
         <v>97</v>
       </c>
       <c r="F4" t="n">
-        <v>17.328</v>
+        <v>17.33</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1786</v>
+        <v>0.17866</v>
       </c>
       <c r="H4" t="n">
-        <v>17.328</v>
+        <v>17.33</v>
       </c>
       <c r="I4" t="n">
-        <v>17.328</v>
+        <v>17.33</v>
       </c>
       <c r="J4" t="n">
-        <v>18.486</v>
+        <v>18.761</v>
       </c>
       <c r="K4" t="n">
         <v>92</v>
@@ -1083,19 +1095,19 @@
         <v>10</v>
       </c>
       <c r="M4" t="n">
-        <v>11.834</v>
+        <v>11.506</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.17</v>
+        <v>-1.78</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.388</v>
+        <v>-0.318</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.935</v>
+        <v>-1.733</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.158</v>
+        <v>1.431</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1116,40 +1128,43 @@
         <v>2.9676</v>
       </c>
       <c r="AC4" t="n">
+        <v>3.0247</v>
+      </c>
+      <c r="AD4" t="n">
         <v>38.4</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>3.386</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
         <v>34</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AG4" t="n">
         <v>55.7</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AH4" t="n">
         <v>19.6</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AK4" t="n">
         <v>57.6</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AL4" t="n">
         <v>65.59999999999999</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AM4" t="n">
         <v>1141</v>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>KO1+KO2+KO3</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>quality_calibrated</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1175,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.176</v>
+        <v>0.176028</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -1184,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.378</v>
+        <v>1.546</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1202,10 +1217,10 @@
         <v>-0.315</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.008</v>
+        <v>-1.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.378</v>
+        <v>1.546</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1231,20 +1246,23 @@
       <c r="AD5" t="n">
         <v>0</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
         <v>1141</v>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>KO2+KO3</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>quality_calibrated</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1270,7 +1288,7 @@
         <v>0.176</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1764</v>
+        <v>0.176367</v>
       </c>
       <c r="H6" t="n">
         <v>0.176</v>
@@ -1279,7 +1297,7 @@
         <v>0.176</v>
       </c>
       <c r="J6" t="n">
-        <v>1.473</v>
+        <v>1.734</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -1288,19 +1306,19 @@
         <v>11</v>
       </c>
       <c r="M6" t="n">
-        <v>12.98</v>
+        <v>12.481</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.34</v>
+        <v>-1.75</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.413</v>
+        <v>-0.309</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.124</v>
+        <v>-1.937</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.296</v>
+        <v>1.557</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1321,37 +1339,40 @@
         <v>0.0333</v>
       </c>
       <c r="AC6" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="AD6" t="n">
         <v>3.8</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AE6" t="n">
         <v>0.038</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AF6" t="n">
         <v>100</v>
       </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
         <v>1141</v>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>KO1+KO3</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>quality_calibrated</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1377,7 +1398,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1762</v>
+        <v>0.176182</v>
       </c>
       <c r="H7" t="n">
         <v>0.622</v>
@@ -1386,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.421</v>
+        <v>2.611</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1404,10 +1425,10 @@
         <v>0.622</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.175</v>
+        <v>-1.068</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.421</v>
+        <v>2.611</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1433,20 +1454,23 @@
       <c r="AD7" t="n">
         <v>0</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
         <v>1141</v>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>KO1+KO2</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>quality_calibrated</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1459,7 +1483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB3"/>
+  <dimension ref="A1:BL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1471,9 +1495,9 @@
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
     <col width="28" customWidth="1" min="13" max="13"/>
     <col width="28" customWidth="1" min="14" max="14"/>
     <col width="28" customWidth="1" min="15" max="15"/>
@@ -1490,8 +1514,8 @@
     <col width="28" customWidth="1" min="26" max="26"/>
     <col width="28" customWidth="1" min="27" max="27"/>
     <col width="28" customWidth="1" min="28" max="28"/>
-    <col width="24" customWidth="1" min="29" max="29"/>
-    <col width="22" customWidth="1" min="30" max="30"/>
+    <col width="28" customWidth="1" min="29" max="29"/>
+    <col width="28" customWidth="1" min="30" max="30"/>
     <col width="28" customWidth="1" min="31" max="31"/>
     <col width="28" customWidth="1" min="32" max="32"/>
     <col width="28" customWidth="1" min="33" max="33"/>
@@ -1500,22 +1524,32 @@
     <col width="28" customWidth="1" min="36" max="36"/>
     <col width="28" customWidth="1" min="37" max="37"/>
     <col width="28" customWidth="1" min="38" max="38"/>
-    <col width="13" customWidth="1" min="39" max="39"/>
-    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="24" customWidth="1" min="39" max="39"/>
+    <col width="22" customWidth="1" min="40" max="40"/>
     <col width="28" customWidth="1" min="41" max="41"/>
     <col width="28" customWidth="1" min="42" max="42"/>
-    <col width="26" customWidth="1" min="43" max="43"/>
-    <col width="22" customWidth="1" min="44" max="44"/>
-    <col width="20" customWidth="1" min="45" max="45"/>
+    <col width="28" customWidth="1" min="43" max="43"/>
+    <col width="28" customWidth="1" min="44" max="44"/>
+    <col width="28" customWidth="1" min="45" max="45"/>
     <col width="28" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
     <col width="28" customWidth="1" min="48" max="48"/>
-    <col width="24" customWidth="1" min="49" max="49"/>
-    <col width="22" customWidth="1" min="50" max="50"/>
+    <col width="13" customWidth="1" min="49" max="49"/>
+    <col width="11" customWidth="1" min="50" max="50"/>
     <col width="28" customWidth="1" min="51" max="51"/>
     <col width="28" customWidth="1" min="52" max="52"/>
-    <col width="28" customWidth="1" min="53" max="53"/>
-    <col width="15" customWidth="1" min="54" max="54"/>
+    <col width="26" customWidth="1" min="53" max="53"/>
+    <col width="22" customWidth="1" min="54" max="54"/>
+    <col width="20" customWidth="1" min="55" max="55"/>
+    <col width="28" customWidth="1" min="56" max="56"/>
+    <col width="28" customWidth="1" min="57" max="57"/>
+    <col width="28" customWidth="1" min="58" max="58"/>
+    <col width="24" customWidth="1" min="59" max="59"/>
+    <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="28" customWidth="1" min="61" max="61"/>
+    <col width="28" customWidth="1" min="62" max="62"/>
+    <col width="28" customWidth="1" min="63" max="63"/>
+    <col width="15" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1556,235 +1590,285 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>unique_density_x1e5_sensitivity_p_welch_log_half_event_vs_Aicda-_-</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>unique_density_x1e5_sensitivity_p_welch_log_third_of_smallest_vs_Aicda-_-</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>unique_density_x1e5_p_mwu_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>combined_density_x1e5_mean</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>combined_density_x1e5_sd</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>combined_density_x1e5_p_welch_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>combined_density_x1e5_p_welch_log_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>combined_density_x1e5_sensitivity_p_welch_log_half_event_vs_Aicda-_-</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>combined_density_x1e5_sensitivity_p_welch_log_third_of_smallest_vs_Aicda-_-</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>combined_density_x1e5_p_mwu_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>single_read_density_x1e5_mean</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>single_read_density_x1e5_sd</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>single_read_density_x1e5_p_welch_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>single_read_density_x1e5_p_welch_log_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>single_read_density_x1e5_sensitivity_p_welch_log_half_event_vs_Aicda-_-</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>single_read_density_x1e5_sensitivity_p_welch_log_third_of_smallest_vs_Aicda-_-</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>single_read_density_x1e5_p_mwu_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>clone_weighted_frequency_x1e3_mean</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>clone_weighted_frequency_x1e3_sd</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>clone_weighted_frequency_x1e3_p_welch_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>clone_weighted_frequency_x1e3_p_welch_log_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>clone_weighted_frequency_x1e3_sensitivity_p_welch_log_half_event_vs_Aicda-_-</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>clone_weighted_frequency_x1e3_sensitivity_p_welch_log_third_of_smallest_vs_Aicda-_-</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
         <is>
           <t>clone_weighted_frequency_x1e3_p_mwu_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>mutation_frequency_x1e3_mean</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>mutation_frequency_x1e3_sd</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>mutation_frequency_x1e3_p_welch_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>mutation_frequency_x1e3_p_welch_log_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>mutation_frequency_x1e3_sensitivity_p_welch_log_half_event_vs_Aicda-_-</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>mutation_frequency_x1e3_sensitivity_p_welch_log_third_of_smallest_vs_Aicda-_-</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
         <is>
           <t>mutation_frequency_x1e3_p_mwu_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>mutated_reads_pct_mean</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>mutated_reads_pct_sd</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>mutated_reads_pct_p_welch_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>mutated_reads_pct_p_welch_log_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>mutated_reads_pct_p_mwu_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>mean_mutations_per_read_mean</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>mean_mutations_per_read_sd</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>mean_mutations_per_read_p_welch_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>mean_mutations_per_read_p_welch_log_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>mean_mutations_per_read_p_mwu_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>pct_GC_mean</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>pct_GC_sd</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>pct_GC_p_welch_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>pct_GC_p_welch_log_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>pct_GC_p_mwu_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>pct_transitions_mean</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>pct_transitions_sd</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>pct_transitions_p_welch_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>pct_transitions_p_welch_log_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>pct_transitions_p_mwu_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>pct_GC_in_WRC_GYW_mean</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>pct_GC_in_WRC_GYW_sd</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>pct_GC_in_WRC_GYW_p_welch_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>pct_GC_in_WRC_GYW_p_welch_log_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>pct_GC_in_WRC_GYW_p_mwu_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>compared_with</t>
         </is>
@@ -1803,138 +1887,168 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>48.288</v>
+        <v>48.287</v>
       </c>
       <c r="E2" t="n">
-        <v>31.7334</v>
+        <v>31.7293</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1190746246118153</v>
+        <v>0.1190534267799172</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006805872120004831</v>
+        <v>0.006804124705209222</v>
       </c>
       <c r="H2" t="n">
+        <v>0.001396305705680895</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0005494375123111762</v>
+      </c>
+      <c r="J2" t="n">
         <v>0.07652250047505924</v>
       </c>
-      <c r="I2" t="n">
-        <v>48.701</v>
-      </c>
-      <c r="J2" t="n">
-        <v>31.7123</v>
-      </c>
       <c r="K2" t="n">
-        <v>0.1180935640364096</v>
+        <v>48.7463</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001270995965637723</v>
+        <v>31.7069</v>
       </c>
       <c r="M2" t="n">
+        <v>0.1178770229747181</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.001270985738019188</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.002399894421242372</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.00445922543964197</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0.1</v>
       </c>
-      <c r="N2" t="n">
-        <v>-0.3397</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.5541</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.7746298200376101</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.7762514638483591</v>
-      </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>-0.062</v>
       </c>
       <c r="S2" t="n">
+        <v>1.3296</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.9462226856859089</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.7538883554404778</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.8210536380203006</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.7391697384255206</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Y2" t="n">
         <v>8.8782</v>
       </c>
-      <c r="T2" t="n">
+      <c r="Z2" t="n">
         <v>5.2015</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AA2" t="n">
         <v>0.09824357232161911</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AB2" t="n">
+        <v>0.002234199790653466</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.0005499154292562147</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.0005235642934090727</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AE2" t="n">
         <v>0.07652250047505924</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AF2" t="n">
         <v>5.7166</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AG2" t="n">
         <v>6.0346</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AH2" t="n">
         <v>0.24315883670197</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AI2" t="n">
+        <v>0.007336850636838427</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.01351972904529697</v>
+      </c>
+      <c r="AK2" t="n">
         <v>0.003569996106257355</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.07652250047505924</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>52.9333</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>34.3862</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.1207694166486803</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.003173652346210436</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.07652250047505924</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>6.5227</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>6.8855</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.2431591267618401</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.003570203885603989</v>
       </c>
       <c r="AL2" t="n">
         <v>0.07652250047505924</v>
       </c>
       <c r="AM2" t="n">
+        <v>52.9333</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>34.3862</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.1207694166486803</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.03317946079819806</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.07652250047505924</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>6.5227</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>6.8855</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.2431591267618401</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.007338225815787472</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.07652250047505924</v>
+      </c>
+      <c r="AW2" t="n">
         <v>32.8</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AX2" t="n">
         <v>1.3748</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>50.0333</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.944</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.48</v>
       </c>
       <c r="BA2" t="n">
         <v>0.5</v>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BB2" t="n">
+        <v>50.0333</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>4.944</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL2" t="inlineStr">
         <is>
           <t>Aicda-/-</t>
         </is>
@@ -1958,52 +2072,52 @@
       <c r="E3" t="n">
         <v>0.1016</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>0.266</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.3206</v>
       </c>
-      <c r="N3" t="n">
-        <v>-0.0353</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.5714</v>
+      <c r="R3" t="n">
+        <v>-0.0007</v>
       </c>
       <c r="S3" t="n">
+        <v>0.5393</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.0183</v>
       </c>
-      <c r="T3" t="n">
+      <c r="Z3" t="n">
         <v>0.0316</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AF3" t="n">
         <v>0.0111</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AG3" t="n">
         <v>0.0192</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AM3" t="n">
         <v>1.2667</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AN3" t="n">
         <v>2.1939</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AR3" t="n">
         <v>0.0127</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AS3" t="n">
         <v>0.0219</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AW3" t="n">
         <v>100</v>
       </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
